--- a/qualis.xlsx
+++ b/qualis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29017"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MEU_GIT\LAFEX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9318B2F5-E1A0-4B97-99DA-B64FE5212E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC2D095-9FA1-4CCB-8120-0B93B616A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4367" uniqueCount="2726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4367" uniqueCount="2727">
   <si>
     <t>ISSN</t>
   </si>
@@ -8201,6 +8201,9 @@
   </si>
   <si>
     <t>Revista voltada para a área de linguistica aplicada. Não se aplica ao LAFEx</t>
+  </si>
+  <si>
+    <t>Revista voltada para a área de imagem corporal e aparencia física. Se aplica ao LAFEx</t>
   </si>
 </sst>
 </file>
@@ -8676,7 +8679,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>2723</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">

--- a/qualis.xlsx
+++ b/qualis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29017"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MEU_GIT\LAFEX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9318B2F5-E1A0-4B97-99DA-B64FE5212E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18FF0B1-7FC1-4336-962F-8F94043BADA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4367" uniqueCount="2726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4367" uniqueCount="2727">
   <si>
     <t>ISSN</t>
   </si>
@@ -8201,6 +8201,9 @@
   </si>
   <si>
     <t>Revista voltada para a área de linguistica aplicada. Não se aplica ao LAFEx</t>
+  </si>
+  <si>
+    <t>Revista voltada para a área de Psicologia (para o estudo científico da imagem corporal e da aparência física humana). Se aplica ao LAFEx.</t>
   </si>
 </sst>
 </file>
@@ -8676,7 +8679,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>2723</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
